--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129613869</v>
+        <v>129614750</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Ärstabodarna, Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629874</v>
+        <v>629950</v>
       </c>
       <c r="R2" t="n">
-        <v>6991489</v>
+        <v>6991576</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -795,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129614750</v>
+        <v>129613869</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,34 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ärstabodarna, Ärstabodarna, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629950</v>
+        <v>629874</v>
       </c>
       <c r="R3" t="n">
-        <v>6991576</v>
+        <v>6991489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +885,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,21 +901,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1146,6 +1146,129 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129616009</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ärstabodarna, Ärstabodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>629978</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6991584</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129614750</v>
+        <v>129613869</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ärstabodarna, Ärstabodarna, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629950</v>
+        <v>629874</v>
       </c>
       <c r="R2" t="n">
-        <v>6991576</v>
+        <v>6991489</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,21 +779,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129613869</v>
+        <v>129614750</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,42 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Ärstabodarna, Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629874</v>
+        <v>629950</v>
       </c>
       <c r="R3" t="n">
-        <v>6991489</v>
+        <v>6991576</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,12 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,6 +886,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129613869</v>
+        <v>129614750</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Ärstabodarna, Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629874</v>
+        <v>629950</v>
       </c>
       <c r="R2" t="n">
-        <v>6991489</v>
+        <v>6991576</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -795,45 +797,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129614750</v>
+        <v>129616882</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ärstabodarna, Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629950</v>
+        <v>630064</v>
       </c>
       <c r="R3" t="n">
-        <v>6991576</v>
+        <v>6991627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,23 +889,9 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129613012</v>
+        <v>129616009</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,42 +919,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Ärstabodarna, Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629921</v>
+        <v>629978</v>
       </c>
       <c r="R4" t="n">
-        <v>6991439</v>
+        <v>6991584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,51 +1031,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616882</v>
+        <v>129613640</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ärstabodarna, Ärstabodarna, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630064</v>
+        <v>629868</v>
       </c>
       <c r="R5" t="n">
-        <v>6991627</v>
+        <v>6991485</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,7 +1128,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616009</v>
+        <v>129613869</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,50 +1157,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ärstabodarna, Ärstabodarna, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629978</v>
+        <v>629874</v>
       </c>
       <c r="R6" t="n">
-        <v>6991584</v>
+        <v>6991489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,6 +1263,126 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129613012</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>629921</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6991439</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129614750</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>129616882</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129616009</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>129613640</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>129613869</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129613012</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,6 +1383,1473 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129676312</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92899</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>630044</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991655</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129676346</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630034</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991656</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129675248</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92899</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630091</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991480</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129674274</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>629899</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991496</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129674787</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78828</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>630000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991592</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129673988</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92899</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>629868</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991485</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129674239</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79070</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>629838</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6991529</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129676017</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>630138</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6991642</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129676185</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92863</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>630154</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6991582</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129674545</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78828</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>629948</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6991557</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På kolade halvstubbe</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129675858</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79070</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>630153</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6991661</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129676698</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92863</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>629935</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6991634</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129674425</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>629984</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6991539</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2851,6 +2851,580 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129676801</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91880</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>629873</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6991585</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129675506</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79661</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>630140</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6991619</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129686034</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97628</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ärstabodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>629782</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6991595</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129674142</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57731</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>629825</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6991511</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129674636</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57891</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>629969</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6991558</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129614750</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>129616882</v>
       </c>
       <c r="B3" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129616009</v>
       </c>
       <c r="B4" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>129613640</v>
       </c>
       <c r="B5" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>129613869</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129613012</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129676312</v>
       </c>
       <c r="B8" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>129676346</v>
       </c>
       <c r="B9" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>129675248</v>
       </c>
       <c r="B10" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>129674274</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,48 +1839,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129674787</v>
+        <v>129673988</v>
       </c>
       <c r="B12" t="n">
-        <v>78828</v>
+        <v>92905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630000</v>
+        <v>629868</v>
       </c>
       <c r="R12" t="n">
-        <v>6991592</v>
+        <v>6991485</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,12 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kolade stubbe</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,48 +1946,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129673988</v>
+        <v>129674787</v>
       </c>
       <c r="B13" t="n">
-        <v>92899</v>
+        <v>78833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629868</v>
+        <v>630000</v>
       </c>
       <c r="R13" t="n">
-        <v>6991485</v>
+        <v>6991592</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2021,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2026,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,7 +2061,7 @@
         <v>129674239</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129676017</v>
       </c>
       <c r="B15" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>129676185</v>
       </c>
       <c r="B16" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>129674545</v>
       </c>
       <c r="B17" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>129675858</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129676698</v>
       </c>
       <c r="B19" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>129674425</v>
       </c>
       <c r="B20" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>129676801</v>
       </c>
       <c r="B21" t="n">
-        <v>91880</v>
+        <v>91885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>129675506</v>
       </c>
       <c r="B22" t="n">
-        <v>79661</v>
+        <v>79665</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,52 +3072,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129686034</v>
+        <v>129674636</v>
       </c>
       <c r="B23" t="n">
-        <v>97628</v>
+        <v>57895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ärstabodarna, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629782</v>
+        <v>629969</v>
       </c>
       <c r="R23" t="n">
-        <v>6991595</v>
+        <v>6991558</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3146,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3165,7 +3170,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3187,7 +3191,7 @@
         <v>129674142</v>
       </c>
       <c r="B24" t="n">
-        <v>57731</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,57 +3315,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129674636</v>
+        <v>129686034</v>
       </c>
       <c r="B25" t="n">
-        <v>57891</v>
+        <v>97639</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629969</v>
+        <v>629782</v>
       </c>
       <c r="R25" t="n">
-        <v>6991558</v>
+        <v>6991595</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3390,7 +3389,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3399,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3409,6 +3408,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3424,6 +3424,123 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129674293</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>629849</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6991492</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129614750</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>129616882</v>
       </c>
       <c r="B3" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129616009</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>129613640</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>129613869</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129613012</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129676312</v>
       </c>
       <c r="B8" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>129676346</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>129675248</v>
       </c>
       <c r="B10" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>129674274</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,48 +1839,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129673988</v>
+        <v>129674787</v>
       </c>
       <c r="B12" t="n">
-        <v>92905</v>
+        <v>78834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629868</v>
+        <v>630000</v>
       </c>
       <c r="R12" t="n">
-        <v>6991485</v>
+        <v>6991592</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,48 +1951,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129674787</v>
+        <v>129673988</v>
       </c>
       <c r="B13" t="n">
-        <v>78833</v>
+        <v>92906</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630000</v>
+        <v>629868</v>
       </c>
       <c r="R13" t="n">
-        <v>6991592</v>
+        <v>6991485</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2016,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,12 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kolade stubbe</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,7 +2061,7 @@
         <v>129674239</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129676017</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>129676185</v>
       </c>
       <c r="B16" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>129674545</v>
       </c>
       <c r="B17" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>129675858</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129676698</v>
       </c>
       <c r="B19" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>129674425</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>129676801</v>
       </c>
       <c r="B21" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>129675506</v>
       </c>
       <c r="B22" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129674636</v>
+        <v>129674142</v>
       </c>
       <c r="B23" t="n">
-        <v>57895</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3105,21 +3105,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629969</v>
+        <v>629825</v>
       </c>
       <c r="R23" t="n">
-        <v>6991558</v>
+        <v>6991511</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3151,7 +3162,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3172,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,10 +3199,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129674142</v>
+        <v>129674636</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,21 +3210,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3221,32 +3232,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629825</v>
+        <v>629969</v>
       </c>
       <c r="R24" t="n">
-        <v>6991511</v>
+        <v>6991558</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,7 +3318,7 @@
         <v>129686034</v>
       </c>
       <c r="B25" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129674293</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3542,6 +3542,499 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129781463</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>630136</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6991547</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129777325</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>629929</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6991507</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129783581</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91593</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>630168</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6991526</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129788829</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>630094</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6991548</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129614750</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>129616882</v>
       </c>
       <c r="B3" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1386,45 +1386,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129676312</v>
+        <v>129676346</v>
       </c>
       <c r="B8" t="n">
-        <v>92906</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630044</v>
+        <v>630034</v>
       </c>
       <c r="R8" t="n">
-        <v>6991655</v>
+        <v>6991656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,50 +1498,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129676346</v>
+        <v>129676312</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>92911</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630034</v>
+        <v>630044</v>
       </c>
       <c r="R9" t="n">
-        <v>6991656</v>
+        <v>6991655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,7 +1608,7 @@
         <v>129675248</v>
       </c>
       <c r="B10" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,48 +1839,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129674787</v>
+        <v>129673988</v>
       </c>
       <c r="B12" t="n">
-        <v>78834</v>
+        <v>92911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630000</v>
+        <v>629868</v>
       </c>
       <c r="R12" t="n">
-        <v>6991592</v>
+        <v>6991485</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,12 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kolade stubbe</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,48 +1946,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129673988</v>
+        <v>129674787</v>
       </c>
       <c r="B13" t="n">
-        <v>92906</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629868</v>
+        <v>630000</v>
       </c>
       <c r="R13" t="n">
-        <v>6991485</v>
+        <v>6991592</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2021,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2026,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,7 +2061,7 @@
         <v>129674239</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,32 +2288,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129676185</v>
+        <v>129674545</v>
       </c>
       <c r="B16" t="n">
-        <v>92870</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630154</v>
+        <v>629948</v>
       </c>
       <c r="R16" t="n">
-        <v>6991582</v>
+        <v>6991557</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,7 +2368,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På kolade halvstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,32 +2400,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129674545</v>
+        <v>129676185</v>
       </c>
       <c r="B17" t="n">
-        <v>78834</v>
+        <v>92875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2430,10 +2435,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629948</v>
+        <v>630154</v>
       </c>
       <c r="R17" t="n">
-        <v>6991557</v>
+        <v>6991582</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,12 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På kolade halvstubbe</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,7 +2510,7 @@
         <v>129675858</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129676698</v>
       </c>
       <c r="B19" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>129676801</v>
       </c>
       <c r="B21" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>129675506</v>
       </c>
       <c r="B22" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>129686034</v>
       </c>
       <c r="B25" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4035,6 +4035,133 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129781851</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>630200</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6991626</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -2288,32 +2288,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129674545</v>
+        <v>129676185</v>
       </c>
       <c r="B16" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629948</v>
+        <v>630154</v>
       </c>
       <c r="R16" t="n">
-        <v>6991557</v>
+        <v>6991582</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,12 +2368,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På kolade halvstubbe</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,32 +2395,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129676185</v>
+        <v>129674545</v>
       </c>
       <c r="B17" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2435,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630154</v>
+        <v>629948</v>
       </c>
       <c r="R17" t="n">
-        <v>6991582</v>
+        <v>6991557</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2475,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På kolade halvstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3072,10 +3072,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129674142</v>
+        <v>129674636</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3105,32 +3105,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629825</v>
+        <v>629969</v>
       </c>
       <c r="R23" t="n">
-        <v>6991511</v>
+        <v>6991558</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3172,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129674636</v>
+        <v>129674142</v>
       </c>
       <c r="B24" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,21 +3199,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3232,21 +3221,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629969</v>
+        <v>629825</v>
       </c>
       <c r="R24" t="n">
-        <v>6991558</v>
+        <v>6991511</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -1839,48 +1839,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129673988</v>
+        <v>129674787</v>
       </c>
       <c r="B12" t="n">
-        <v>92911</v>
+        <v>78839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629868</v>
+        <v>630000</v>
       </c>
       <c r="R12" t="n">
-        <v>6991485</v>
+        <v>6991592</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,48 +1951,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129674787</v>
+        <v>129673988</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>92911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630000</v>
+        <v>629868</v>
       </c>
       <c r="R13" t="n">
-        <v>6991592</v>
+        <v>6991485</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2016,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,12 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kolade stubbe</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3072,10 +3072,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129674636</v>
+        <v>129674142</v>
       </c>
       <c r="B23" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3105,21 +3105,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629969</v>
+        <v>629825</v>
       </c>
       <c r="R23" t="n">
-        <v>6991558</v>
+        <v>6991511</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3151,7 +3162,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3172,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,10 +3199,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129674142</v>
+        <v>129674636</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,21 +3210,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3221,32 +3232,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629825</v>
+        <v>629969</v>
       </c>
       <c r="R24" t="n">
-        <v>6991511</v>
+        <v>6991558</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -1386,50 +1386,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129676346</v>
+        <v>129676312</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>92911</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630034</v>
+        <v>630044</v>
       </c>
       <c r="R8" t="n">
-        <v>6991656</v>
+        <v>6991655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,45 +1493,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129676312</v>
+        <v>129676346</v>
       </c>
       <c r="B9" t="n">
-        <v>92911</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630044</v>
+        <v>630034</v>
       </c>
       <c r="R9" t="n">
-        <v>6991655</v>
+        <v>6991656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1839,48 +1839,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129674787</v>
+        <v>129673988</v>
       </c>
       <c r="B12" t="n">
-        <v>78839</v>
+        <v>92911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630000</v>
+        <v>629868</v>
       </c>
       <c r="R12" t="n">
-        <v>6991592</v>
+        <v>6991485</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,12 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kolade stubbe</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,48 +1946,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129673988</v>
+        <v>129674787</v>
       </c>
       <c r="B13" t="n">
-        <v>92911</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629868</v>
+        <v>630000</v>
       </c>
       <c r="R13" t="n">
-        <v>6991485</v>
+        <v>6991592</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2021,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2026,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>129616882</v>
       </c>
       <c r="B3" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129676312</v>
       </c>
       <c r="B8" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>129675248</v>
       </c>
       <c r="B10" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129673988</v>
       </c>
       <c r="B12" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>129676185</v>
       </c>
       <c r="B16" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129676698</v>
       </c>
       <c r="B19" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>129676801</v>
       </c>
       <c r="B21" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>129686034</v>
       </c>
       <c r="B25" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>129783581</v>
       </c>
       <c r="B29" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>129616882</v>
       </c>
       <c r="B3" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1386,45 +1386,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129676312</v>
+        <v>129676346</v>
       </c>
       <c r="B8" t="n">
-        <v>92915</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630044</v>
+        <v>630034</v>
       </c>
       <c r="R8" t="n">
-        <v>6991655</v>
+        <v>6991656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,50 +1498,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129676346</v>
+        <v>129676312</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>92917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630034</v>
+        <v>630044</v>
       </c>
       <c r="R9" t="n">
-        <v>6991656</v>
+        <v>6991655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,7 +1608,7 @@
         <v>129675248</v>
       </c>
       <c r="B10" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129673988</v>
       </c>
       <c r="B12" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>129676185</v>
       </c>
       <c r="B16" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129676698</v>
       </c>
       <c r="B19" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>129676801</v>
       </c>
       <c r="B21" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>129686034</v>
       </c>
       <c r="B25" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>129783581</v>
       </c>
       <c r="B29" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -1386,50 +1386,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129676346</v>
+        <v>129676312</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>92917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630034</v>
+        <v>630044</v>
       </c>
       <c r="R8" t="n">
-        <v>6991656</v>
+        <v>6991655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,45 +1493,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129676312</v>
+        <v>129676346</v>
       </c>
       <c r="B9" t="n">
-        <v>92917</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630044</v>
+        <v>630034</v>
       </c>
       <c r="R9" t="n">
-        <v>6991655</v>
+        <v>6991656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 29699-2025 artfynd.xlsx
+++ b/artfynd/A 29699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,48 +797,61 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129616882</v>
+        <v>129616009</v>
       </c>
       <c r="B3" t="n">
-        <v>92917</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ärstabodarna, Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630064</v>
+        <v>629978</v>
       </c>
       <c r="R3" t="n">
-        <v>6991627</v>
+        <v>6991584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +902,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129616009</v>
+        <v>129613640</v>
       </c>
       <c r="B4" t="n">
         <v>57896</v>
@@ -936,36 +948,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ärstabodarna, Ärstabodarna, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629978</v>
+        <v>629868</v>
       </c>
       <c r="R4" t="n">
-        <v>6991584</v>
+        <v>6991485</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129613640</v>
+        <v>129613869</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,23 +1068,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629868</v>
+        <v>629874</v>
       </c>
       <c r="R5" t="n">
-        <v>6991485</v>
+        <v>6991489</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129613869</v>
+        <v>129613012</v>
       </c>
       <c r="B6" t="n">
         <v>57736</v>
@@ -1189,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629874</v>
+        <v>629921</v>
       </c>
       <c r="R6" t="n">
-        <v>6991489</v>
+        <v>6991439</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1266,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129613012</v>
+        <v>129676346</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,42 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629921</v>
+        <v>630034</v>
       </c>
       <c r="R7" t="n">
-        <v>6991439</v>
+        <v>6991656</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,27 +1345,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,45 +1387,65 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129676312</v>
+        <v>129674274</v>
       </c>
       <c r="B8" t="n">
-        <v>92917</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630044</v>
+        <v>629899</v>
       </c>
       <c r="R8" t="n">
-        <v>6991655</v>
+        <v>6991496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129676346</v>
+        <v>129674787</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,39 +1525,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630034</v>
+        <v>630000</v>
       </c>
       <c r="R9" t="n">
-        <v>6991656</v>
+        <v>6991592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,32 +1626,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129675248</v>
+        <v>129674239</v>
       </c>
       <c r="B10" t="n">
-        <v>92917</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1640,10 +1661,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630091</v>
+        <v>629838</v>
       </c>
       <c r="R10" t="n">
-        <v>6991480</v>
+        <v>6991529</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129674274</v>
+        <v>129676017</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,34 +1744,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1767,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629899</v>
+        <v>630138</v>
       </c>
       <c r="R11" t="n">
-        <v>6991496</v>
+        <v>6991642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1829,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,48 +1856,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129673988</v>
+        <v>129674545</v>
       </c>
       <c r="B12" t="n">
-        <v>92917</v>
+        <v>78839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629868</v>
+        <v>629948</v>
       </c>
       <c r="R12" t="n">
-        <v>6991485</v>
+        <v>6991557</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1936,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolade halvstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,32 +1968,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129674787</v>
+        <v>129676185</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1981,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630000</v>
+        <v>630154</v>
       </c>
       <c r="R13" t="n">
-        <v>6991592</v>
+        <v>6991582</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,12 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kolade stubbe</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,7 +2075,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129674239</v>
+        <v>129675858</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -2093,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629838</v>
+        <v>630153</v>
       </c>
       <c r="R14" t="n">
-        <v>6991529</v>
+        <v>6991661</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,6 +2166,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2165,61 +2197,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129676017</v>
+        <v>129676698</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>92881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630138</v>
+        <v>629935</v>
       </c>
       <c r="R15" t="n">
-        <v>6991642</v>
+        <v>6991634</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,45 +2304,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129676185</v>
+        <v>129674425</v>
       </c>
       <c r="B16" t="n">
-        <v>92881</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630154</v>
+        <v>629984</v>
       </c>
       <c r="R16" t="n">
-        <v>6991582</v>
+        <v>6991539</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,7 +2389,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,10 +2421,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129674545</v>
+        <v>129676801</v>
       </c>
       <c r="B17" t="n">
-        <v>78839</v>
+        <v>91897</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,21 +2432,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2430,10 +2456,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629948</v>
+        <v>629873</v>
       </c>
       <c r="R17" t="n">
-        <v>6991557</v>
+        <v>6991585</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,12 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På kolade halvstubbe</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,10 +2528,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675858</v>
+        <v>129675506</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2518,21 +2539,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2542,10 +2563,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630153</v>
+        <v>630140</v>
       </c>
       <c r="R18" t="n">
-        <v>6991661</v>
+        <v>6991619</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2608,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolade stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,21 +2624,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2629,45 +2640,65 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129676698</v>
+        <v>129674142</v>
       </c>
       <c r="B19" t="n">
-        <v>92881</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629935</v>
+        <v>629825</v>
       </c>
       <c r="R19" t="n">
-        <v>6991634</v>
+        <v>6991511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,10 +2767,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129674425</v>
+        <v>129674636</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,27 +2778,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2776,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629984</v>
+        <v>629969</v>
       </c>
       <c r="R20" t="n">
-        <v>6991539</v>
+        <v>6991558</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,12 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,48 +2883,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129676801</v>
+        <v>129686034</v>
       </c>
       <c r="B21" t="n">
-        <v>91897</v>
+        <v>97661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629873</v>
+        <v>629782</v>
       </c>
       <c r="R21" t="n">
-        <v>6991585</v>
+        <v>6991595</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2923,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2933,7 +2967,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,6 +2976,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2960,10 +2995,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129675506</v>
+        <v>129674293</v>
       </c>
       <c r="B22" t="n">
-        <v>79671</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,34 +3006,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630140</v>
+        <v>629849</v>
       </c>
       <c r="R22" t="n">
-        <v>6991619</v>
+        <v>6991492</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3030,7 +3070,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3040,12 +3080,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På kolade stubbe</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,10 +3112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129674142</v>
+        <v>129781463</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,54 +3123,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629825</v>
+        <v>630136</v>
       </c>
       <c r="R23" t="n">
-        <v>6991511</v>
+        <v>6991547</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3157,22 +3185,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,10 +3227,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129674636</v>
+        <v>129777325</v>
       </c>
       <c r="B24" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,43 +3238,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629969</v>
+        <v>629929</v>
       </c>
       <c r="R24" t="n">
-        <v>6991558</v>
+        <v>6991507</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,22 +3295,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,8 +3319,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3315,52 +3353,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129686034</v>
+        <v>129783581</v>
       </c>
       <c r="B25" t="n">
-        <v>97651</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ärstabodarna, Ång</t>
+          <t>Andersmyrberget, Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629782</v>
+        <v>630168</v>
       </c>
       <c r="R25" t="n">
-        <v>6991595</v>
+        <v>6991526</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3384,22 +3421,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3411,6 +3448,21 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3427,10 +3479,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129674293</v>
+        <v>129788829</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3438,42 +3490,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629849</v>
+        <v>630094</v>
       </c>
       <c r="R26" t="n">
-        <v>6991492</v>
+        <v>6991548</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3497,27 +3547,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,8 +3571,24 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3544,10 +3605,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129781463</v>
+        <v>129781851</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,45 +3616,57 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Andersmyrberget, Ång</t>
+          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630136</v>
+        <v>630200</v>
       </c>
       <c r="R27" t="n">
-        <v>6991547</v>
+        <v>6991626</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3622,7 +3695,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3632,7 +3705,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3659,10 +3732,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129777325</v>
+        <v>129676312</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>92919</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3670,21 +3743,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3697,10 +3770,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>629929</v>
+        <v>630044</v>
       </c>
       <c r="R28" t="n">
-        <v>6991507</v>
+        <v>6991655</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3727,22 +3800,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3754,21 +3827,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3785,10 +3843,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129783581</v>
+        <v>129675248</v>
       </c>
       <c r="B29" t="n">
-        <v>91599</v>
+        <v>92919</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,21 +3854,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3823,10 +3881,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630168</v>
+        <v>630091</v>
       </c>
       <c r="R29" t="n">
-        <v>6991526</v>
+        <v>6991480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3853,22 +3911,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,21 +3938,6 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3911,10 +3954,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788829</v>
+        <v>129616882</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>92919</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3922,21 +3965,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3945,17 +3988,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
+          <t>Ärstabodarna, Ärstabodarna, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630094</v>
+        <v>630064</v>
       </c>
       <c r="R30" t="n">
-        <v>6991548</v>
+        <v>6991627</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3979,22 +4022,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4007,21 +4050,6 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4034,133 +4062,6 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>129781851</v>
-      </c>
-      <c r="B31" t="n">
-        <v>57736</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Andersmyrberget, Lövsjön, Ytterlännäs s:n, Ång</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>630200</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6991626</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Dal</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
